--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4635E4FC-92C1-8A49-802E-EC7EB4BA5EA8}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFC0166D-8105-C94E-9079-F4303A09D233}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="8980" windowWidth="22000" windowHeight="12620" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="1500" yWindow="-21100" windowWidth="27500" windowHeight="19660" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="204">
   <si>
     <t>Publication CodeName</t>
   </si>
@@ -317,9 +317,6 @@
     <t>Kverkova_etal_2018</t>
   </si>
   <si>
-    <t>birds compared to mammals - this can be used to check all above cell counts</t>
-  </si>
-  <si>
     <t>ManyPrimates_etal_2022</t>
   </si>
   <si>
@@ -450,13 +447,215 @@
   </si>
   <si>
     <t>wait for Project Kaskan</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.7554/eLife.77875</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Supplementary file 3</t>
+  </si>
+  <si>
+    <t>10.1093/jmammal/gyz043</t>
+  </si>
+  <si>
+    <t>Supplementary Data SD1</t>
+  </si>
+  <si>
+    <t>Note: related Item(s) included in folder</t>
+  </si>
+  <si>
+    <t>Supplementary Data SD2</t>
+  </si>
+  <si>
+    <t>10.1007/s004220000205</t>
+  </si>
+  <si>
+    <t>Figure 3</t>
+  </si>
+  <si>
+    <t>10.1038/s41467-020-14356-3</t>
+  </si>
+  <si>
+    <t>Supplementary Data 3</t>
+  </si>
+  <si>
+    <t>10.1159/000452856</t>
+  </si>
+  <si>
+    <t>Table S1</t>
+  </si>
+  <si>
+    <t>ERRATUM !</t>
+  </si>
+  <si>
+    <t>10.1523/JNEUROSCI.2339-19.2020</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>10.1159/000124401</t>
+  </si>
+  <si>
+    <t>10.1159/000121494</t>
+  </si>
+  <si>
+    <t>10.1038/srep24528</t>
+  </si>
+  <si>
+    <t>Table I</t>
+  </si>
+  <si>
+    <t>Table 6.1</t>
+  </si>
+  <si>
+    <t>10.1159/000437413</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Table 3</t>
+  </si>
+  <si>
+    <t>Table 4</t>
+  </si>
+  <si>
+    <t>Table 5</t>
+  </si>
+  <si>
+    <t>Table 6</t>
+  </si>
+  <si>
+    <t>Table 1. Cerebral cortex</t>
+  </si>
+  <si>
+    <t>Table 2. Cerebellum</t>
+  </si>
+  <si>
+    <t>Table 3. RoB</t>
+  </si>
+  <si>
+    <t>Table 6. Relative distributions of mass and numbers of neurons across brain structures</t>
+  </si>
+  <si>
+    <t>Table 4. Olfactory bulb</t>
+  </si>
+  <si>
+    <t>Table 5. Whole brain</t>
+  </si>
+  <si>
+    <t>10.1002/cne.24985</t>
+  </si>
+  <si>
+    <t>TABLE 1 Dataset</t>
+  </si>
+  <si>
+    <t>TABLE 2 Numbers of neurons and neuronal density (neurons/mg)</t>
+  </si>
+  <si>
+    <t>TABLE 1</t>
+  </si>
+  <si>
+    <t>TABLE 2</t>
+  </si>
+  <si>
+    <t>region size</t>
+  </si>
+  <si>
+    <t>Cell numbers</t>
+  </si>
+  <si>
+    <t>10.1037/0735-7036.115.1.29</t>
+  </si>
+  <si>
+    <t>Table 2 The Five Play Scores and Relative Brain Sizes for the Species of Muroid Rodents Examined</t>
+  </si>
+  <si>
+    <t>Table 3 The Play Scores and Relative Brain ( EQ) and Neocortex Sizes for the Marsupials Examined</t>
+  </si>
+  <si>
+    <t>Table 1 Encephalization Quotients (EQs) and Play Scores for 15 Mammalian Orders</t>
+  </si>
+  <si>
+    <t>Table 4 Play Scores and Relative Brain and Neocortex Sizes for the Primates Examined</t>
+  </si>
+  <si>
+    <t>10.3389/fnana.2017.00118</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-018-26062-8</t>
+  </si>
+  <si>
+    <t>Table S5</t>
+  </si>
+  <si>
+    <t>African mole-rats (Bathyergidae)</t>
+  </si>
+  <si>
+    <t>Table S5. Numbers of neurons in the whole brain and the major brain divisions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table S1. Brain mass and brain region volumes </t>
+  </si>
+  <si>
+    <t>10.26451/abc.09.04.06.2022</t>
+  </si>
+  <si>
+    <t>https://github.com/ManyPrimates/mp1_short_term_memory/raw/master/data/species_predictors.xlsx</t>
+  </si>
+  <si>
+    <t>data/species_predictors.xlsx</t>
+  </si>
+  <si>
+    <t>10.1098/rspb.2017.1765</t>
+  </si>
+  <si>
+    <t>ARTICLE DOI if different</t>
+  </si>
+  <si>
+    <t>10.6084/m9.figshare.c.3899422.v1</t>
+  </si>
+  <si>
+    <t>Dataset 1</t>
+  </si>
+  <si>
+    <t>https://figshare.com/ndownloader/files/9479092</t>
+  </si>
+  <si>
+    <t>10.1159/000075672</t>
+  </si>
+  <si>
+    <t>Table 4. GLI values for each cortical layer</t>
+  </si>
+  <si>
+    <t>Table 5. Species mean values for 10 GLI
+profile feature vectors</t>
+  </si>
+  <si>
+    <t>10.1080/09524622.2021.1905065</t>
+  </si>
+  <si>
+    <t>Figure 1</t>
+  </si>
+  <si>
+    <t>10.3389/fncir.2013.00030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -493,6 +692,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -515,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -523,6 +728,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -838,884 +1047,1512 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.1640625" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="16.1640625" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="10" width="22.1640625" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="14" max="14" width="46.5" customWidth="1"/>
+    <col min="2" max="3" width="31.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.1640625" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="13" max="14" width="22.1640625" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" customWidth="1"/>
+    <col min="18" max="18" width="46.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="G2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>19</v>
       </c>
-      <c r="N2" t="s">
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="O2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="str">
-        <f>IF(E3="N", D3, E3)</f>
+      <c r="J3" t="str">
+        <f>IF(I3="N", H3, I3)</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
-      <c r="G3" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" t="s">
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="I3" t="s">
+      <c r="M3" t="s">
         <v>28</v>
       </c>
-      <c r="K3" t="s">
+      <c r="O3" t="s">
         <v>29</v>
       </c>
-      <c r="L3" t="s">
+      <c r="P3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" t="s">
+      <c r="R3" t="s">
         <v>31</v>
       </c>
-      <c r="O3" t="s">
+      <c r="S3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>36</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
+      <c r="L4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K4" t="s">
+      <c r="O4" t="s">
         <v>40</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4" t="s">
         <v>41</v>
       </c>
-      <c r="N4" t="s">
+      <c r="R4" t="s">
         <v>42</v>
       </c>
-      <c r="O4" t="s">
+      <c r="S4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
         <v>44</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="str">
-        <f>IF(E5="Y", E5, D5)</f>
+      <c r="J5" t="str">
+        <f>IF(I5="Y", I5, H5)</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
-      <c r="G5" t="s">
+      <c r="K5" t="s">
         <v>46</v>
       </c>
-      <c r="H5" t="s">
+      <c r="L5" t="s">
         <v>27</v>
       </c>
-      <c r="I5" t="s">
+      <c r="M5" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K5" t="s">
+      <c r="O5" t="s">
         <v>49</v>
       </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
         <v>30</v>
       </c>
-      <c r="O5" t="s">
+      <c r="S5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H6" t="s">
         <v>127</v>
       </c>
-      <c r="B6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="I6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" t="s">
+      <c r="K6" t="s">
         <v>37</v>
       </c>
-      <c r="H6" t="s">
-        <v>136</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" t="s">
-        <v>131</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
+        <v>134</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" t="s">
         <v>130</v>
       </c>
-      <c r="N6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6" t="s">
+        <v>129</v>
+      </c>
+      <c r="R6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" t="s">
+      <c r="G7" s="3"/>
+      <c r="H7" t="s">
         <v>51</v>
       </c>
-      <c r="E7" t="s">
+      <c r="I7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="str">
-        <f t="shared" ref="F7:F23" si="0">IF(E7="Y", E7, D7)</f>
+      <c r="J7" t="str">
+        <f t="shared" ref="J7:J34" si="0">IF(I7="Y", I7, H7)</f>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
-      <c r="G7" t="s">
+      <c r="K7" t="s">
         <v>46</v>
       </c>
-      <c r="H7" t="s">
+      <c r="L7" t="s">
         <v>27</v>
       </c>
-      <c r="I7" t="s">
+      <c r="M7" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K7" t="s">
+      <c r="O7" t="s">
         <v>53</v>
       </c>
-      <c r="L7" t="s">
+      <c r="P7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" t="s">
+      <c r="Q7" t="s">
         <v>54</v>
       </c>
-      <c r="N7" t="s">
-        <v>133</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="R7" t="s">
+        <v>132</v>
+      </c>
+      <c r="S7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>56</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" t="s">
+      <c r="G8" s="3"/>
+      <c r="H8" t="s">
         <v>57</v>
       </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
         <v>35</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>58</v>
       </c>
-      <c r="G8" t="s">
+      <c r="K8" t="s">
         <v>59</v>
       </c>
-      <c r="H8" t="s">
+      <c r="L8" t="s">
         <v>60</v>
       </c>
-      <c r="I8" t="s">
+      <c r="M8" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8" t="s">
         <v>62</v>
       </c>
-      <c r="L8" t="s">
+      <c r="P8" t="s">
         <v>63</v>
       </c>
-      <c r="O8" t="s">
+      <c r="S8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="5"/>
-      <c r="F9">
+      <c r="G9" s="3"/>
+      <c r="H9" s="5"/>
+      <c r="J9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" t="s">
+      <c r="K9" t="s">
         <v>37</v>
       </c>
-      <c r="H9" t="s">
+      <c r="L9" t="s">
         <v>27</v>
       </c>
-      <c r="K9" t="s">
+      <c r="O9" t="s">
         <v>62</v>
       </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
         <v>63</v>
       </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" t="s">
+      <c r="B10" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" t="s">
         <v>70</v>
       </c>
-      <c r="E10" t="s">
+      <c r="I10" t="s">
         <v>35</v>
       </c>
-      <c r="G10" t="s">
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="K10" t="s">
         <v>71</v>
       </c>
-      <c r="H10" t="s">
+      <c r="L10" t="s">
         <v>27</v>
       </c>
-      <c r="I10" t="s">
+      <c r="M10" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K10" t="s">
-        <v>132</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
+        <v>131</v>
+      </c>
+      <c r="R10" t="s">
         <v>73</v>
       </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="F11">
+      <c r="G11" s="3"/>
+      <c r="J11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" t="s">
+      <c r="K11" t="s">
         <v>37</v>
       </c>
-      <c r="H11" t="s">
+      <c r="L11" t="s">
         <v>27</v>
       </c>
-      <c r="K11" t="s">
+      <c r="O11" t="s">
         <v>76</v>
       </c>
-      <c r="M11" t="s">
+      <c r="Q11" t="s">
         <v>77</v>
       </c>
-      <c r="O11" t="s">
+      <c r="S11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="5"/>
-      <c r="F12">
+      <c r="G12" s="3"/>
+      <c r="H12" s="5"/>
+      <c r="J12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" t="s">
+      <c r="K12" t="s">
         <v>37</v>
       </c>
-      <c r="H12" t="s">
+      <c r="L12" t="s">
         <v>27</v>
       </c>
-      <c r="K12" t="s">
+      <c r="O12" t="s">
         <v>76</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="5"/>
-      <c r="F13">
+      <c r="G13" s="3"/>
+      <c r="H13" s="5"/>
+      <c r="J13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" t="s">
+      <c r="K13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" t="s">
         <v>27</v>
       </c>
-      <c r="K13" t="s">
+      <c r="O13" t="s">
         <v>81</v>
       </c>
-      <c r="O13" t="s">
+      <c r="S13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="5"/>
-      <c r="F14">
+      <c r="G14" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="J14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" t="s">
+      <c r="K14" t="s">
         <v>37</v>
       </c>
-      <c r="H14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" t="s">
         <v>62</v>
       </c>
-      <c r="O14" t="s">
+      <c r="S14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="5"/>
-      <c r="F15">
+        <v>82</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="J15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" t="s">
+      <c r="K15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" t="s">
         <v>27</v>
       </c>
-      <c r="K15" t="s">
+      <c r="O15" t="s">
         <v>62</v>
       </c>
-      <c r="O15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="S15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="5"/>
-      <c r="F16">
+        <v>82</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="J16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" t="s">
+      <c r="K16" t="s">
         <v>37</v>
       </c>
-      <c r="H16" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" t="s">
-        <v>88</v>
+      <c r="L16" t="s">
+        <v>27</v>
       </c>
       <c r="O16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="S16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="5"/>
-      <c r="F17">
+        <v>82</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="J17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" t="s">
         <v>27</v>
       </c>
-      <c r="K17" t="s">
+      <c r="O17" t="s">
         <v>62</v>
       </c>
-      <c r="O17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="S17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="5"/>
-      <c r="F18">
+        <v>82</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="J18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" t="s">
+      <c r="K18" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" t="s">
         <v>27</v>
       </c>
-      <c r="K18" t="s">
+      <c r="O18" t="s">
         <v>62</v>
       </c>
-      <c r="O18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="S18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="5"/>
-      <c r="F19">
+        <v>82</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="J19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" t="s">
+      <c r="K19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" t="s">
         <v>27</v>
       </c>
-      <c r="K19" t="s">
-        <v>96</v>
-      </c>
-      <c r="M19" t="s">
-        <v>97</v>
-      </c>
       <c r="O19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="S19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="5"/>
-      <c r="F20">
+        <v>85</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="J20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" t="s">
+      <c r="K20" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" t="s">
         <v>27</v>
       </c>
-      <c r="K20" t="s">
-        <v>99</v>
-      </c>
-      <c r="L20" t="s">
-        <v>30</v>
-      </c>
-      <c r="M20" t="s">
-        <v>29</v>
-      </c>
       <c r="O20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+      <c r="S20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="5"/>
-      <c r="F21">
+        <v>85</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="J21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" t="s">
+      <c r="K21" t="s">
         <v>37</v>
       </c>
-      <c r="H21" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" t="s">
-        <v>101</v>
-      </c>
       <c r="L21" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="O21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="S21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="5"/>
-      <c r="F22">
+        <v>87</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="J22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" t="s">
+      <c r="K22" t="s">
         <v>37</v>
       </c>
-      <c r="H22" t="s">
-        <v>103</v>
-      </c>
-      <c r="K22" t="s">
-        <v>104</v>
+      <c r="L22" t="s">
+        <v>27</v>
       </c>
       <c r="O22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="S22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="5"/>
-      <c r="F23">
+        <v>87</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="J23">
+        <f t="shared" ref="J23:J24" si="1">IF(I23="Y", I23, H23)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" t="s">
+        <v>88</v>
+      </c>
+      <c r="S23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" t="s">
+        <v>88</v>
+      </c>
+      <c r="S24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="J25">
+        <f t="shared" ref="J25" si="2">IF(I25="Y", I25, H25)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>37</v>
+      </c>
+      <c r="L25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" t="s">
+        <v>88</v>
+      </c>
+      <c r="S25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="5"/>
+      <c r="J26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" t="s">
+      <c r="K26" t="s">
+        <v>37</v>
+      </c>
+      <c r="L26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" t="s">
+        <v>62</v>
+      </c>
+      <c r="S26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" t="s">
+        <v>177</v>
+      </c>
+      <c r="S27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="J28">
+        <f t="shared" ref="J28" si="3">IF(I28="Y", I28, H28)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" t="s">
+        <v>178</v>
+      </c>
+      <c r="S28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="5"/>
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" t="s">
+        <v>47</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O29" t="s">
+        <v>95</v>
+      </c>
+      <c r="P29" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>96</v>
+      </c>
+      <c r="S29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="5"/>
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" t="s">
+        <v>47</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="O30" t="s">
+        <v>98</v>
+      </c>
+      <c r="P30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="J31">
+        <f t="shared" ref="J31" si="4">IF(I31="Y", I31, H31)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31" t="s">
+        <v>83</v>
+      </c>
+      <c r="O31" t="s">
+        <v>100</v>
+      </c>
+      <c r="P31" t="s">
+        <v>63</v>
+      </c>
+      <c r="S31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="J32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" t="s">
+        <v>83</v>
+      </c>
+      <c r="O32" t="s">
+        <v>100</v>
+      </c>
+      <c r="P32" t="s">
+        <v>63</v>
+      </c>
+      <c r="S32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="5"/>
+      <c r="J33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>37</v>
+      </c>
+      <c r="L33" t="s">
+        <v>102</v>
+      </c>
+      <c r="O33" t="s">
+        <v>103</v>
+      </c>
+      <c r="S33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="5"/>
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
         <v>71</v>
       </c>
-      <c r="H23" t="s">
+      <c r="L34" t="s">
         <v>27</v>
       </c>
-      <c r="K23" t="s">
+      <c r="O34" t="s">
+        <v>105</v>
+      </c>
+      <c r="S34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>106</v>
       </c>
-      <c r="O23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+      <c r="B45" t="s">
         <v>109</v>
       </c>
-      <c r="B34" t="s">
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+      <c r="B46" t="s">
         <v>111</v>
       </c>
-      <c r="B35" t="s">
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+      <c r="B47" t="s">
         <v>113</v>
       </c>
-      <c r="B36" t="s">
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+      <c r="B48" t="s">
         <v>115</v>
       </c>
-      <c r="B37" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+      <c r="B49" t="s">
         <v>117</v>
       </c>
-      <c r="B38" t="s">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
+      <c r="B50" t="s">
         <v>119</v>
       </c>
-      <c r="B39" t="s">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+      <c r="B51" t="s">
         <v>121</v>
       </c>
-      <c r="B40" t="s">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
+      <c r="B52" t="s">
         <v>123</v>
       </c>
-      <c r="B41" t="s">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+      <c r="B53" t="s">
         <v>125</v>
       </c>
-      <c r="B42" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>129</v>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O23">
-    <sortCondition ref="A2:A23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S34">
+    <sortCondition ref="A2:A34"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{08AF1EFA-E780-B045-ACEC-E23D010DA150}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{794936F9-140A-1247-A81C-F8FE376C8D8E}"/>
     <hyperlink ref="A7" r:id="rId3" xr:uid="{9C37E554-41C9-7149-8F06-F73D52457581}"/>
-    <hyperlink ref="A8" r:id="rId4" xr:uid="{AB8C2E9E-7D33-A24B-81BE-DE337580587D}"/>
-    <hyperlink ref="A9" r:id="rId5" xr:uid="{9ED38DAE-F888-9E4B-8CCF-E97CA3B12E5F}"/>
-    <hyperlink ref="A12" r:id="rId6" xr:uid="{ADE4A84F-D86D-8A41-993A-8527CE289E8B}"/>
-    <hyperlink ref="A13" r:id="rId7" xr:uid="{8DC8D3BA-92D2-544F-8A3C-722643E317EB}"/>
-    <hyperlink ref="A14" r:id="rId8" xr:uid="{4B82E5F9-8EA9-2846-84B0-E1DDA6F65B6C}"/>
-    <hyperlink ref="A15" r:id="rId9" xr:uid="{61188575-9E2A-8D4D-B25F-D193F49C46B9}"/>
-    <hyperlink ref="A16" r:id="rId10" xr:uid="{5D0245D2-4411-1447-B9E3-27B3DE3EAE05}"/>
-    <hyperlink ref="A17" r:id="rId11" xr:uid="{C9F83F19-A018-7544-8AB4-F93361A516FA}"/>
-    <hyperlink ref="A18" r:id="rId12" xr:uid="{569E788C-7890-EA49-BB81-66C6CE7D4E7B}"/>
-    <hyperlink ref="A19" r:id="rId13" xr:uid="{9E14452E-FE71-B64D-9DA0-01A0EB31E798}"/>
-    <hyperlink ref="A20" r:id="rId14" xr:uid="{26BAF204-91AF-EB46-AE21-08CA9E04B1F1}"/>
-    <hyperlink ref="A21" r:id="rId15" xr:uid="{3A50421D-44C2-8643-9578-AB5B7B0E6A1F}"/>
-    <hyperlink ref="A22" r:id="rId16" xr:uid="{9131733F-F59E-4F48-ADB4-9B4D5B4885E1}"/>
-    <hyperlink ref="A23" r:id="rId17" xr:uid="{D2CB73B3-66C1-9549-B2F2-2546E44AA117}"/>
-    <hyperlink ref="J4" r:id="rId18" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{E0793C32-CFF3-BA46-91D5-CE57A5CB5249}"/>
-    <hyperlink ref="A4" r:id="rId19" xr:uid="{452B100A-1F40-614E-825E-9765F9342088}"/>
-    <hyperlink ref="A5" r:id="rId20" xr:uid="{98E74710-97A9-9649-B34C-7CCF86AAA074}"/>
-    <hyperlink ref="J5" r:id="rId21" xr:uid="{0C8D4DAC-C617-2547-BF75-D17B07FAB104}"/>
-    <hyperlink ref="J7" r:id="rId22" xr:uid="{5C533C8B-7E31-6247-B07A-DA36A2ECB804}"/>
-    <hyperlink ref="J8" r:id="rId23" xr:uid="{C7A27B14-F289-2345-8125-B9AE06601A7B}"/>
-    <hyperlink ref="J10" r:id="rId24" xr:uid="{BC8CFBF1-94B9-B04B-B168-9B969B0A4C7D}"/>
-    <hyperlink ref="A10" r:id="rId25" xr:uid="{79F5B0C6-1DEA-430F-B9C6-88856489C235}"/>
-    <hyperlink ref="A11" r:id="rId26" xr:uid="{9C507629-3611-4B53-9850-0E6E8EA5B62C}"/>
-    <hyperlink ref="A6" r:id="rId27" xr:uid="{3BF2A8C1-257E-E641-B0D5-EC8D36A925AD}"/>
+    <hyperlink ref="A9" r:id="rId4" xr:uid="{9ED38DAE-F888-9E4B-8CCF-E97CA3B12E5F}"/>
+    <hyperlink ref="A12" r:id="rId5" xr:uid="{ADE4A84F-D86D-8A41-993A-8527CE289E8B}"/>
+    <hyperlink ref="A13" r:id="rId6" xr:uid="{8DC8D3BA-92D2-544F-8A3C-722643E317EB}"/>
+    <hyperlink ref="A14" r:id="rId7" xr:uid="{4B82E5F9-8EA9-2846-84B0-E1DDA6F65B6C}"/>
+    <hyperlink ref="A21" r:id="rId8" xr:uid="{61188575-9E2A-8D4D-B25F-D193F49C46B9}"/>
+    <hyperlink ref="A22" r:id="rId9" xr:uid="{5D0245D2-4411-1447-B9E3-27B3DE3EAE05}"/>
+    <hyperlink ref="A26" r:id="rId10" xr:uid="{C9F83F19-A018-7544-8AB4-F93361A516FA}"/>
+    <hyperlink ref="A27" r:id="rId11" xr:uid="{569E788C-7890-EA49-BB81-66C6CE7D4E7B}"/>
+    <hyperlink ref="A29" r:id="rId12" xr:uid="{9E14452E-FE71-B64D-9DA0-01A0EB31E798}"/>
+    <hyperlink ref="A30" r:id="rId13" xr:uid="{26BAF204-91AF-EB46-AE21-08CA9E04B1F1}"/>
+    <hyperlink ref="A32" r:id="rId14" xr:uid="{3A50421D-44C2-8643-9578-AB5B7B0E6A1F}"/>
+    <hyperlink ref="A33" r:id="rId15" xr:uid="{9131733F-F59E-4F48-ADB4-9B4D5B4885E1}"/>
+    <hyperlink ref="A34" r:id="rId16" xr:uid="{D2CB73B3-66C1-9549-B2F2-2546E44AA117}"/>
+    <hyperlink ref="N4" r:id="rId17" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{E0793C32-CFF3-BA46-91D5-CE57A5CB5249}"/>
+    <hyperlink ref="A4" r:id="rId18" xr:uid="{452B100A-1F40-614E-825E-9765F9342088}"/>
+    <hyperlink ref="A5" r:id="rId19" xr:uid="{98E74710-97A9-9649-B34C-7CCF86AAA074}"/>
+    <hyperlink ref="N5" r:id="rId20" xr:uid="{0C8D4DAC-C617-2547-BF75-D17B07FAB104}"/>
+    <hyperlink ref="N7" r:id="rId21" xr:uid="{5C533C8B-7E31-6247-B07A-DA36A2ECB804}"/>
+    <hyperlink ref="N8" r:id="rId22" xr:uid="{C7A27B14-F289-2345-8125-B9AE06601A7B}"/>
+    <hyperlink ref="N10" r:id="rId23" xr:uid="{BC8CFBF1-94B9-B04B-B168-9B969B0A4C7D}"/>
+    <hyperlink ref="A10" r:id="rId24" xr:uid="{79F5B0C6-1DEA-430F-B9C6-88856489C235}"/>
+    <hyperlink ref="A11" r:id="rId25" xr:uid="{9C507629-3611-4B53-9850-0E6E8EA5B62C}"/>
+    <hyperlink ref="A6" r:id="rId26" xr:uid="{3BF2A8C1-257E-E641-B0D5-EC8D36A925AD}"/>
+    <hyperlink ref="A16" r:id="rId27" xr:uid="{F826F04B-0439-E84F-83B3-B0D195BF50EF}"/>
+    <hyperlink ref="A18" r:id="rId28" xr:uid="{688B790E-47B4-2849-BB0C-CEC015B9538E}"/>
+    <hyperlink ref="A20" r:id="rId29" xr:uid="{F121AB2E-DAC0-AA48-86FF-6A32662819BC}"/>
+    <hyperlink ref="A23" r:id="rId30" xr:uid="{F47913E8-5984-534D-8340-9DFCDD92BCBC}"/>
+    <hyperlink ref="A24" r:id="rId31" xr:uid="{FB11CE9D-6A0D-504E-A8DD-16CF6170F8A3}"/>
+    <hyperlink ref="A25" r:id="rId32" xr:uid="{55C6822C-AE98-584E-B896-A75BBE393403}"/>
+    <hyperlink ref="A28" r:id="rId33" xr:uid="{43B67C9C-0C3B-4E4F-9EEE-225D557AE13D}"/>
+    <hyperlink ref="N29" r:id="rId34" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
+    <hyperlink ref="N30" r:id="rId35" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
+    <hyperlink ref="A31" r:id="rId36" xr:uid="{DE23E549-C543-F745-A3C2-B0DDB1E2B18A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -1952,32 +2789,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6D714A-5497-420A-9146-5640EA73F0F4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1994,4 +2826,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECFF182C-239F-A04F-A0D5-6167A03F69D3}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B0E5DA-E804-7E44-9E71-F75CA95E4194}"/>
   <bookViews>
-    <workbookView xWindow="45280" yWindow="-5060" windowWidth="38960" windowHeight="20480" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="42300" yWindow="-5960" windowWidth="38960" windowHeight="20480" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="213">
   <si>
     <t>Publication CodeName</t>
   </si>
@@ -667,6 +667,15 @@
   </si>
   <si>
     <t>mostly secondary</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table1.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table1.csv</t>
+  </si>
+  <si>
+    <t>https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf</t>
   </si>
 </sst>
 </file>
@@ -1350,6 +1359,10 @@
       <c r="I6" t="s">
         <v>34</v>
       </c>
+      <c r="J6" t="str">
+        <f t="shared" ref="J6:J34" si="0">IF(I6="Y", I6, H6)</f>
+        <v>Y</v>
+      </c>
       <c r="K6" t="s">
         <v>36</v>
       </c>
@@ -1393,7 +1406,7 @@
         <v>24</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" ref="J7:J34" si="0">IF(I7="Y", I7, H7)</f>
+        <f t="shared" si="0"/>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
       <c r="K7" t="s">
@@ -1577,6 +1590,9 @@
       <c r="H11" t="s">
         <v>208</v>
       </c>
+      <c r="I11" t="s">
+        <v>34</v>
+      </c>
       <c r="J11" t="s">
         <v>207</v>
       </c>
@@ -1688,16 +1704,26 @@
       <c r="G14" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H14" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" t="s">
+        <v>211</v>
       </c>
       <c r="K14" t="s">
         <v>36</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="O14" t="s">
         <v>61</v>
@@ -1735,6 +1761,12 @@
       <c r="L15" t="s">
         <v>26</v>
       </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="O15" t="s">
         <v>61</v>
       </c>
@@ -1771,6 +1803,12 @@
       <c r="L16" t="s">
         <v>26</v>
       </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="O16" t="s">
         <v>61</v>
       </c>
@@ -1807,6 +1845,12 @@
       <c r="L17" t="s">
         <v>26</v>
       </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="O17" t="s">
         <v>61</v>
       </c>
@@ -1843,6 +1887,12 @@
       <c r="L18" t="s">
         <v>26</v>
       </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="O18" t="s">
         <v>61</v>
       </c>
@@ -1878,6 +1928,12 @@
       </c>
       <c r="L19" t="s">
         <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="O19" t="s">
         <v>61</v>
@@ -2585,12 +2641,23 @@
     <hyperlink ref="N29" r:id="rId34" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
     <hyperlink ref="N30" r:id="rId35" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
     <hyperlink ref="A31" r:id="rId36" xr:uid="{DE23E549-C543-F745-A3C2-B0DDB1E2B18A}"/>
+    <hyperlink ref="N14" r:id="rId37" xr:uid="{9534F0D1-7C63-EC4F-921C-5D21474866A4}"/>
+    <hyperlink ref="N15:N19" r:id="rId38" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -2827,15 +2894,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2848,6 +2906,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6D714A-5497-420A-9146-5640EA73F0F4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2866,27 +2932,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B0E5DA-E804-7E44-9E71-F75CA95E4194}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0050A280-8D89-8942-BF38-BC48EAE125AF}"/>
   <bookViews>
     <workbookView xWindow="42300" yWindow="-5960" windowWidth="38960" windowHeight="20480" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="218">
   <si>
     <t>Publication CodeName</t>
   </si>
@@ -242,9 +242,6 @@
     <t>Finlay_etal_2006</t>
   </si>
   <si>
-    <t>in progress</t>
-  </si>
-  <si>
     <t>Finlay_2006_primary_or_equivalent.xlsx</t>
   </si>
   <si>
@@ -524,9 +521,6 @@
     <t>Table 5</t>
   </si>
   <si>
-    <t>Table 6</t>
-  </si>
-  <si>
     <t>Table 1. Cerebral cortex</t>
   </si>
   <si>
@@ -534,9 +528,6 @@
   </si>
   <si>
     <t>Table 3. RoB</t>
-  </si>
-  <si>
-    <t>Table 6. Relative distributions of mass and numbers of neurons across brain structures</t>
   </si>
   <si>
     <t>Table 4. Olfactory bulb</t>
@@ -676,13 +667,37 @@
   </si>
   <si>
     <t>https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table2.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table3.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table4.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table5.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table2.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table3.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table4.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table5.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -725,6 +740,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -747,7 +770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -762,6 +785,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1077,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.1640625" customWidth="1"/>
@@ -1102,16 +1126,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -1126,7 +1150,7 @@
         <v>4</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
@@ -1191,14 +1215,14 @@
         <v>21</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -1241,15 +1265,15 @@
         <v>31</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -1293,15 +1317,15 @@
         <v>31</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G5" t="s">
         <v>43</v>
@@ -1340,47 +1364,47 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I6" t="s">
         <v>34</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" ref="J6:J34" si="0">IF(I6="Y", I6, H6)</f>
+        <f t="shared" ref="J6:J33" si="0">IF(I6="Y", I6, H6)</f>
         <v>Y</v>
       </c>
       <c r="K6" t="s">
         <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -1388,15 +1412,15 @@
         <v>49</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" t="s">
@@ -1431,7 +1455,7 @@
         <v>53</v>
       </c>
       <c r="R7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S7" t="s">
         <v>54</v>
@@ -1442,17 +1466,17 @@
         <v>55</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>150</v>
-      </c>
       <c r="F8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" t="s">
@@ -1491,11 +1515,11 @@
         <v>64</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="2" t="s">
@@ -1528,19 +1552,19 @@
         <v>67</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
         <v>34</v>
@@ -1550,7 +1574,7 @@
         <v>Y</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -1559,13 +1583,13 @@
         <v>37</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O10" t="s">
+        <v>129</v>
+      </c>
+      <c r="R10" t="s">
         <v>71</v>
-      </c>
-      <c r="O10" t="s">
-        <v>130</v>
-      </c>
-      <c r="R10" t="s">
-        <v>72</v>
       </c>
       <c r="S10" t="s">
         <v>20</v>
@@ -1573,28 +1597,28 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I11" t="s">
         <v>34</v>
       </c>
       <c r="J11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K11" t="s">
         <v>36</v>
@@ -1603,16 +1627,16 @@
         <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O11" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q11" t="s">
         <v>75</v>
-      </c>
-      <c r="P11" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>76</v>
       </c>
       <c r="S11" t="s">
         <v>20</v>
@@ -1620,18 +1644,18 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="5"/>
@@ -1646,7 +1670,7 @@
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S12" t="s">
         <v>20</v>
@@ -1654,18 +1678,18 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="5"/>
@@ -1680,7 +1704,7 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S13" t="s">
         <v>42</v>
@@ -1688,30 +1712,30 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J14" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K14" t="s">
         <v>36</v>
@@ -1723,37 +1747,38 @@
         <v>37</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O14" t="s">
         <v>61</v>
       </c>
       <c r="S14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="J15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J15" t="s">
+        <v>214</v>
       </c>
       <c r="K15" t="s">
         <v>36</v>
@@ -1765,37 +1790,38 @@
         <v>37</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O15" t="s">
         <v>61</v>
       </c>
       <c r="S15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="J16">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J16" t="s">
+        <v>215</v>
       </c>
       <c r="K16" t="s">
         <v>36</v>
@@ -1807,37 +1833,38 @@
         <v>37</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O16" t="s">
         <v>61</v>
       </c>
       <c r="S16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="J17">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>164</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J17" t="s">
+        <v>216</v>
       </c>
       <c r="K17" t="s">
         <v>36</v>
@@ -1849,37 +1876,38 @@
         <v>37</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O17" t="s">
         <v>61</v>
       </c>
       <c r="S17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" s="5"/>
-      <c r="J18">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J18" t="s">
+        <v>217</v>
       </c>
       <c r="K18" t="s">
         <v>36</v>
@@ -1891,32 +1919,32 @@
         <v>37</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O18" t="s">
         <v>61</v>
       </c>
       <c r="S18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>166</v>
+      <c r="F19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="H19" s="5"/>
       <c r="J19">
@@ -1929,36 +1957,30 @@
       <c r="L19" t="s">
         <v>26</v>
       </c>
-      <c r="M19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="O19" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
       <c r="S19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="B20" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H20" s="5"/>
       <c r="J20">
@@ -1972,29 +1994,29 @@
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="B21" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="E21" s="7"/>
-      <c r="F21" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>171</v>
+      <c r="F21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="H21" s="5"/>
       <c r="J21">
@@ -2008,33 +2030,33 @@
         <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="S21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H22" s="5"/>
       <c r="J22">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J22:J23" si="1">IF(I22="Y", I22, H22)</f>
         <v>0</v>
       </c>
       <c r="K22" t="s">
@@ -2044,18 +2066,18 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
+        <v>86</v>
+      </c>
+      <c r="S22" t="s">
         <v>87</v>
-      </c>
-      <c r="S22" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7" t="s">
@@ -2063,14 +2085,14 @@
       </c>
       <c r="E23" s="7"/>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H23" s="5"/>
       <c r="J23">
-        <f t="shared" ref="J23:J24" si="1">IF(I23="Y", I23, H23)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K23" t="s">
@@ -2080,18 +2102,18 @@
         <v>26</v>
       </c>
       <c r="O23" t="s">
+        <v>86</v>
+      </c>
+      <c r="S23" t="s">
         <v>87</v>
-      </c>
-      <c r="S23" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
@@ -2099,14 +2121,14 @@
       </c>
       <c r="E24" s="7"/>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H24" s="5"/>
       <c r="J24">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J24" si="2">IF(I24="Y", I24, H24)</f>
         <v>0</v>
       </c>
       <c r="K24" t="s">
@@ -2116,33 +2138,31 @@
         <v>26</v>
       </c>
       <c r="O24" t="s">
+        <v>86</v>
+      </c>
+      <c r="S24" t="s">
         <v>87</v>
       </c>
-      <c r="S24" t="s">
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="B25" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="E25" s="7"/>
-      <c r="F25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="F25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="5"/>
       <c r="J25">
-        <f t="shared" ref="J25" si="2">IF(I25="Y", I25, H25)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K25" t="s">
@@ -2152,28 +2172,30 @@
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="S25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="J26">
         <f t="shared" si="0"/>
@@ -2186,33 +2208,33 @@
         <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
       <c r="S26" t="s">
-        <v>90</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H27" s="5"/>
       <c r="J27">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J27" si="3">IF(I27="Y", I27, H27)</f>
         <v>0</v>
       </c>
       <c r="K27" t="s">
@@ -2222,10 +2244,10 @@
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S27" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
@@ -2233,51 +2255,63 @@
         <v>91</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C28" s="7"/>
-      <c r="D28" s="7" t="s">
-        <v>183</v>
+      <c r="D28" s="9" t="s">
+        <v>186</v>
       </c>
       <c r="E28" s="7"/>
-      <c r="F28" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="F28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="5"/>
       <c r="J28">
-        <f t="shared" ref="J28" si="3">IF(I28="Y", I28, H28)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L28" t="s">
         <v>26</v>
       </c>
+      <c r="M28" t="s">
+        <v>46</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="O28" t="s">
-        <v>175</v>
+        <v>93</v>
+      </c>
+      <c r="P28" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>94</v>
       </c>
       <c r="S28" t="s">
-        <v>184</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="9" t="s">
-        <v>189</v>
+      <c r="D29" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="E29" s="7"/>
-      <c r="F29" t="s">
-        <v>93</v>
+      <c r="F29" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="5"/>
@@ -2295,16 +2329,16 @@
         <v>46</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P29" t="s">
         <v>29</v>
       </c>
       <c r="Q29" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="S29" t="s">
         <v>42</v>
@@ -2312,47 +2346,38 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>190</v>
-      </c>
+      <c r="C30" s="7"/>
       <c r="D30" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="3"/>
       <c r="H30" s="5"/>
       <c r="J30">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J30" si="4">IF(I30="Y", I30, H30)</f>
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" t="s">
-        <v>46</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>194</v>
+        <v>81</v>
       </c>
       <c r="O30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="S30" t="s">
         <v>42</v>
@@ -2360,10 +2385,10 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7" t="s">
@@ -2371,24 +2396,24 @@
       </c>
       <c r="E31" s="7"/>
       <c r="F31" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>196</v>
+        <v>92</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="H31" s="5"/>
       <c r="J31">
-        <f t="shared" ref="J31" si="4">IF(I31="Y", I31, H31)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K31" t="s">
         <v>36</v>
       </c>
       <c r="L31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P31" t="s">
         <v>62</v>
@@ -2399,22 +2424,20 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>195</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="E32" s="7"/>
-      <c r="F32" t="s">
-        <v>93</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>197</v>
-      </c>
+      <c r="F32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="5"/>
       <c r="J32">
         <f t="shared" si="0"/>
@@ -2424,32 +2447,29 @@
         <v>36</v>
       </c>
       <c r="L32" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="O32" t="s">
-        <v>99</v>
-      </c>
-      <c r="P32" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="S32" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="E33" s="7"/>
-      <c r="F33" s="2" t="s">
-        <v>78</v>
+      <c r="F33" t="s">
+        <v>92</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="5"/>
@@ -2458,50 +2478,21 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="L33" t="s">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="5"/>
-      <c r="J34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
-        <v>70</v>
-      </c>
-      <c r="L34" t="s">
-        <v>26</v>
-      </c>
-      <c r="O34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>104</v>
-      </c>
-      <c r="S34" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
@@ -2510,98 +2501,93 @@
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="4" t="s">
         <v>106</v>
+      </c>
+      <c r="B44" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B51" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
         <v>123</v>
       </c>
+    </row>
+    <row r="53" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A53" s="10" t="s">
+        <v>199</v>
+      </c>
       <c r="B53" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A54" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B54" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>127</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S34">
-    <sortCondition ref="A2:A34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S33">
+    <sortCondition ref="A2:A33"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -2612,15 +2598,15 @@
     <hyperlink ref="A12" r:id="rId5" xr:uid="{ADE4A84F-D86D-8A41-993A-8527CE289E8B}"/>
     <hyperlink ref="A13" r:id="rId6" xr:uid="{8DC8D3BA-92D2-544F-8A3C-722643E317EB}"/>
     <hyperlink ref="A14" r:id="rId7" xr:uid="{4B82E5F9-8EA9-2846-84B0-E1DDA6F65B6C}"/>
-    <hyperlink ref="A21" r:id="rId8" xr:uid="{61188575-9E2A-8D4D-B25F-D193F49C46B9}"/>
-    <hyperlink ref="A22" r:id="rId9" xr:uid="{5D0245D2-4411-1447-B9E3-27B3DE3EAE05}"/>
-    <hyperlink ref="A26" r:id="rId10" xr:uid="{C9F83F19-A018-7544-8AB4-F93361A516FA}"/>
-    <hyperlink ref="A27" r:id="rId11" xr:uid="{569E788C-7890-EA49-BB81-66C6CE7D4E7B}"/>
-    <hyperlink ref="A29" r:id="rId12" xr:uid="{9E14452E-FE71-B64D-9DA0-01A0EB31E798}"/>
-    <hyperlink ref="A30" r:id="rId13" xr:uid="{26BAF204-91AF-EB46-AE21-08CA9E04B1F1}"/>
-    <hyperlink ref="A32" r:id="rId14" xr:uid="{3A50421D-44C2-8643-9578-AB5B7B0E6A1F}"/>
-    <hyperlink ref="A33" r:id="rId15" xr:uid="{9131733F-F59E-4F48-ADB4-9B4D5B4885E1}"/>
-    <hyperlink ref="A34" r:id="rId16" xr:uid="{D2CB73B3-66C1-9549-B2F2-2546E44AA117}"/>
+    <hyperlink ref="A20" r:id="rId8" xr:uid="{61188575-9E2A-8D4D-B25F-D193F49C46B9}"/>
+    <hyperlink ref="A21" r:id="rId9" xr:uid="{5D0245D2-4411-1447-B9E3-27B3DE3EAE05}"/>
+    <hyperlink ref="A25" r:id="rId10" xr:uid="{C9F83F19-A018-7544-8AB4-F93361A516FA}"/>
+    <hyperlink ref="A26" r:id="rId11" xr:uid="{569E788C-7890-EA49-BB81-66C6CE7D4E7B}"/>
+    <hyperlink ref="A28" r:id="rId12" xr:uid="{9E14452E-FE71-B64D-9DA0-01A0EB31E798}"/>
+    <hyperlink ref="A29" r:id="rId13" xr:uid="{26BAF204-91AF-EB46-AE21-08CA9E04B1F1}"/>
+    <hyperlink ref="A31" r:id="rId14" xr:uid="{3A50421D-44C2-8643-9578-AB5B7B0E6A1F}"/>
+    <hyperlink ref="A32" r:id="rId15" xr:uid="{9131733F-F59E-4F48-ADB4-9B4D5B4885E1}"/>
+    <hyperlink ref="A33" r:id="rId16" xr:uid="{D2CB73B3-66C1-9549-B2F2-2546E44AA117}"/>
     <hyperlink ref="N4" r:id="rId17" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{E0793C32-CFF3-BA46-91D5-CE57A5CB5249}"/>
     <hyperlink ref="A4" r:id="rId18" xr:uid="{452B100A-1F40-614E-825E-9765F9342088}"/>
     <hyperlink ref="A5" r:id="rId19" xr:uid="{98E74710-97A9-9649-B34C-7CCF86AAA074}"/>
@@ -2633,16 +2619,16 @@
     <hyperlink ref="A6" r:id="rId26" xr:uid="{3BF2A8C1-257E-E641-B0D5-EC8D36A925AD}"/>
     <hyperlink ref="A16" r:id="rId27" xr:uid="{F826F04B-0439-E84F-83B3-B0D195BF50EF}"/>
     <hyperlink ref="A18" r:id="rId28" xr:uid="{688B790E-47B4-2849-BB0C-CEC015B9538E}"/>
-    <hyperlink ref="A20" r:id="rId29" xr:uid="{F121AB2E-DAC0-AA48-86FF-6A32662819BC}"/>
-    <hyperlink ref="A23" r:id="rId30" xr:uid="{F47913E8-5984-534D-8340-9DFCDD92BCBC}"/>
-    <hyperlink ref="A24" r:id="rId31" xr:uid="{FB11CE9D-6A0D-504E-A8DD-16CF6170F8A3}"/>
-    <hyperlink ref="A25" r:id="rId32" xr:uid="{55C6822C-AE98-584E-B896-A75BBE393403}"/>
-    <hyperlink ref="A28" r:id="rId33" xr:uid="{43B67C9C-0C3B-4E4F-9EEE-225D557AE13D}"/>
-    <hyperlink ref="N29" r:id="rId34" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
-    <hyperlink ref="N30" r:id="rId35" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
-    <hyperlink ref="A31" r:id="rId36" xr:uid="{DE23E549-C543-F745-A3C2-B0DDB1E2B18A}"/>
+    <hyperlink ref="A19" r:id="rId29" xr:uid="{F121AB2E-DAC0-AA48-86FF-6A32662819BC}"/>
+    <hyperlink ref="A22" r:id="rId30" xr:uid="{F47913E8-5984-534D-8340-9DFCDD92BCBC}"/>
+    <hyperlink ref="A23" r:id="rId31" xr:uid="{FB11CE9D-6A0D-504E-A8DD-16CF6170F8A3}"/>
+    <hyperlink ref="A24" r:id="rId32" xr:uid="{55C6822C-AE98-584E-B896-A75BBE393403}"/>
+    <hyperlink ref="A27" r:id="rId33" xr:uid="{43B67C9C-0C3B-4E4F-9EEE-225D557AE13D}"/>
+    <hyperlink ref="N28" r:id="rId34" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
+    <hyperlink ref="N29" r:id="rId35" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
+    <hyperlink ref="A30" r:id="rId36" xr:uid="{DE23E549-C543-F745-A3C2-B0DDB1E2B18A}"/>
     <hyperlink ref="N14" r:id="rId37" xr:uid="{9534F0D1-7C63-EC4F-921C-5D21474866A4}"/>
-    <hyperlink ref="N15:N19" r:id="rId38" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
+    <hyperlink ref="N15:N18" r:id="rId38" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2658,6 +2644,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -2894,17 +2891,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
@@ -2914,6 +2900,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6D714A-5497-420A-9146-5640EA73F0F4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2930,21 +2933,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67144838-569A-A743-8DAD-DB58B14466F4}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7FFE0DE-8451-EF46-80D8-00BF56164272}"/>
   <bookViews>
-    <workbookView xWindow="34960" yWindow="-5960" windowWidth="50800" windowHeight="17920" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30660" windowHeight="15420" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="230">
   <si>
     <t>Publication CodeName</t>
   </si>
@@ -697,6 +697,36 @@
   </si>
   <si>
     <t>dossantos_etal_2017_tables1.csv</t>
+  </si>
+  <si>
+    <t>pdf online</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2020_Table1_primary_or_equivalent.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2020_Table1.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2020_Table2.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2020_Table2_primary_or_equivalent.csv</t>
+  </si>
+  <si>
+    <t>docx</t>
+  </si>
+  <si>
+    <t>https://static-content.springer.com/esm/art%3A10.1038%2Fs41598-018-26062-8/MediaObjects/41598_2018_26062_MOESM1_ESM.docx</t>
+  </si>
+  <si>
+    <t>Kverkova_etal_2018_TableS1.csv</t>
+  </si>
+  <si>
+    <t>Kverkova_etal_2018_TableS5.csv</t>
+  </si>
+  <si>
+    <t>docx online</t>
   </si>
 </sst>
 </file>
@@ -1116,15 +1146,17 @@
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="19.1640625" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" customWidth="1"/>
     <col min="10" max="10" width="31" customWidth="1"/>
     <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
-    <col min="13" max="14" width="22.1640625" customWidth="1"/>
+    <col min="13" max="13" width="22.1640625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
     <col min="15" max="15" width="12.33203125" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" customWidth="1"/>
+    <col min="18" max="18" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -1541,7 +1573,7 @@
         <v>218</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -1786,6 +1818,9 @@
       <c r="H15" s="5" t="s">
         <v>208</v>
       </c>
+      <c r="I15" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J15" t="s">
         <v>212</v>
       </c>
@@ -1829,6 +1864,9 @@
       <c r="H16" s="12" t="s">
         <v>209</v>
       </c>
+      <c r="I16" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J16" t="s">
         <v>213</v>
       </c>
@@ -1872,6 +1910,9 @@
       <c r="H17" s="5" t="s">
         <v>210</v>
       </c>
+      <c r="I17" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J17" t="s">
         <v>214</v>
       </c>
@@ -1915,6 +1956,9 @@
       <c r="H18" s="5" t="s">
         <v>211</v>
       </c>
+      <c r="I18" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J18" t="s">
         <v>215</v>
       </c>
@@ -1949,16 +1993,20 @@
         <v>167</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="2" t="s">
-        <v>64</v>
+      <c r="F19" t="s">
+        <v>198</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="J19">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H19" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" t="s">
+        <v>222</v>
       </c>
       <c r="K19" t="s">
         <v>36</v>
@@ -1988,22 +2036,29 @@
         <v>168</v>
       </c>
       <c r="E20" s="7"/>
-      <c r="F20" s="2" t="s">
-        <v>64</v>
+      <c r="F20" t="s">
+        <v>198</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="J20">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H20" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" t="s">
+        <v>223</v>
       </c>
       <c r="K20" t="s">
         <v>36</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
+      </c>
+      <c r="M20" t="s">
+        <v>130</v>
       </c>
       <c r="O20" t="s">
         <v>170</v>
@@ -2202,22 +2257,27 @@
         <v>146</v>
       </c>
       <c r="E26" s="7"/>
-      <c r="F26" s="2" t="s">
-        <v>64</v>
+      <c r="F26" t="s">
+        <v>198</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>181</v>
       </c>
       <c r="H26" s="5"/>
-      <c r="J26">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="J26" t="s">
+        <v>227</v>
       </c>
       <c r="K26" t="s">
-        <v>36</v>
+        <v>225</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="O26" t="s">
         <v>169</v>
@@ -2238,22 +2298,27 @@
         <v>178</v>
       </c>
       <c r="E27" s="7"/>
-      <c r="F27" s="2" t="s">
-        <v>64</v>
+      <c r="F27" t="s">
+        <v>198</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
       <c r="H27" s="5"/>
-      <c r="J27">
-        <f t="shared" ref="J27" si="3">IF(I27="Y", I27, H27)</f>
-        <v>0</v>
+      <c r="J27" t="s">
+        <v>228</v>
       </c>
       <c r="K27" t="s">
-        <v>36</v>
+        <v>229</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="O27" t="s">
         <v>170</v>
@@ -2376,7 +2441,7 @@
       </c>
       <c r="H30" s="5"/>
       <c r="J30">
-        <f t="shared" ref="J30" si="4">IF(I30="Y", I30, H30)</f>
+        <f t="shared" ref="J30" si="3">IF(I30="Y", I30, H30)</f>
         <v>0</v>
       </c>
       <c r="K30" t="s">
@@ -2641,6 +2706,8 @@
     <hyperlink ref="A30" r:id="rId36" xr:uid="{DE23E549-C543-F745-A3C2-B0DDB1E2B18A}"/>
     <hyperlink ref="N14" r:id="rId37" xr:uid="{9534F0D1-7C63-EC4F-921C-5D21474866A4}"/>
     <hyperlink ref="N15:N18" r:id="rId38" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
+    <hyperlink ref="N27" r:id="rId39" xr:uid="{FD223821-8B74-3345-B8A9-FA7536E78F2E}"/>
+    <hyperlink ref="N26" r:id="rId40" xr:uid="{8FF3DE15-909D-F043-B90F-3D2A3402F9DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7FFE0DE-8451-EF46-80D8-00BF56164272}"/>
+  <xr:revisionPtr revIDLastSave="287" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7CCB523-DD9C-2142-9C4D-294B5C6C4BAA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30660" windowHeight="15420" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="1960" yWindow="760" windowWidth="30660" windowHeight="15420" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="232">
   <si>
     <t>Publication CodeName</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>DosSantos_etal_2020</t>
-  </si>
-  <si>
-    <t>redo and record steps</t>
   </si>
   <si>
     <t>microglia</t>
@@ -727,6 +724,15 @@
   </si>
   <si>
     <t>docx online</t>
+  </si>
+  <si>
+    <t>units</t>
+  </si>
+  <si>
+    <t>JardimMesseder_etal_2017_Table1.csv</t>
+  </si>
+  <si>
+    <t>JardimMesseder_etal_2017_Table1_primary_or_equivalent.csv</t>
   </si>
 </sst>
 </file>
@@ -1164,16 +1170,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -1188,7 +1194,7 @@
         <v>4</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
@@ -1253,14 +1259,14 @@
         <v>21</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -1303,15 +1309,15 @@
         <v>31</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -1355,15 +1361,15 @@
         <v>31</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G5" t="s">
         <v>43</v>
@@ -1402,21 +1408,21 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I6" t="s">
         <v>34</v>
@@ -1429,20 +1435,20 @@
         <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -1450,15 +1456,15 @@
         <v>49</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" t="s">
@@ -1493,7 +1499,7 @@
         <v>53</v>
       </c>
       <c r="R7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S7" t="s">
         <v>54</v>
@@ -1504,17 +1510,17 @@
         <v>55</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="F8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H8" t="s">
         <v>56</v>
@@ -1523,7 +1529,7 @@
         <v>34</v>
       </c>
       <c r="J8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K8" t="s">
         <v>57</v>
@@ -1552,28 +1558,28 @@
         <v>63</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
       </c>
       <c r="J9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -1585,27 +1591,27 @@
         <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
         <v>34</v>
@@ -1615,7 +1621,7 @@
         <v>Y</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -1624,13 +1630,13 @@
         <v>37</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" t="s">
+        <v>215</v>
+      </c>
+      <c r="R10" t="s">
         <v>69</v>
-      </c>
-      <c r="O10" t="s">
-        <v>216</v>
-      </c>
-      <c r="R10" t="s">
-        <v>70</v>
       </c>
       <c r="S10" t="s">
         <v>20</v>
@@ -1638,28 +1644,28 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I11" t="s">
         <v>34</v>
       </c>
       <c r="J11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K11" t="s">
         <v>36</v>
@@ -1668,16 +1674,16 @@
         <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O11" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q11" t="s">
         <v>73</v>
-      </c>
-      <c r="P11" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>74</v>
       </c>
       <c r="S11" t="s">
         <v>20</v>
@@ -1685,18 +1691,18 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="5"/>
@@ -1711,7 +1717,7 @@
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S12" t="s">
         <v>20</v>
@@ -1719,18 +1725,18 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="5"/>
@@ -1745,7 +1751,7 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S13" t="s">
         <v>42</v>
@@ -1753,30 +1759,30 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K14" t="s">
         <v>36</v>
@@ -1788,41 +1794,41 @@
         <v>37</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O14" t="s">
         <v>60</v>
       </c>
       <c r="S14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K15" t="s">
         <v>36</v>
@@ -1834,41 +1840,41 @@
         <v>37</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O15" t="s">
         <v>60</v>
       </c>
       <c r="S15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K16" t="s">
         <v>36</v>
@@ -1880,41 +1886,41 @@
         <v>37</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O16" t="s">
         <v>60</v>
       </c>
       <c r="S16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K17" t="s">
         <v>36</v>
@@ -1926,41 +1932,41 @@
         <v>37</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O17" t="s">
         <v>60</v>
       </c>
       <c r="S17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K18" t="s">
         <v>36</v>
@@ -1972,41 +1978,41 @@
         <v>37</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O18" t="s">
         <v>60</v>
       </c>
       <c r="S18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K19" t="s">
         <v>36</v>
@@ -2015,41 +2021,41 @@
         <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K20" t="s">
         <v>36</v>
@@ -2058,32 +2064,32 @@
         <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H21" s="5"/>
       <c r="J21">
@@ -2097,29 +2103,29 @@
         <v>26</v>
       </c>
       <c r="O21" t="s">
+        <v>84</v>
+      </c>
+      <c r="S21" t="s">
         <v>85</v>
-      </c>
-      <c r="S21" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H22" s="5"/>
       <c r="J22">
@@ -2133,29 +2139,29 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
+        <v>84</v>
+      </c>
+      <c r="S22" t="s">
         <v>85</v>
-      </c>
-      <c r="S22" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H23" s="5"/>
       <c r="J23">
@@ -2169,29 +2175,29 @@
         <v>26</v>
       </c>
       <c r="O23" t="s">
+        <v>84</v>
+      </c>
+      <c r="S23" t="s">
         <v>85</v>
-      </c>
-      <c r="S23" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H24" s="5"/>
       <c r="J24">
@@ -2205,32 +2211,36 @@
         <v>26</v>
       </c>
       <c r="O24" t="s">
+        <v>84</v>
+      </c>
+      <c r="S24" t="s">
         <v>85</v>
-      </c>
-      <c r="S24" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="2" t="s">
-        <v>64</v>
+      <c r="F25" t="s">
+        <v>197</v>
       </c>
       <c r="G25" s="3"/>
-      <c r="H25" s="5"/>
-      <c r="J25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H25" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" t="s">
+        <v>230</v>
       </c>
       <c r="K25" t="s">
         <v>36</v>
@@ -2238,37 +2248,43 @@
       <c r="L25" t="s">
         <v>26</v>
       </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
       <c r="O25" t="s">
         <v>60</v>
       </c>
       <c r="S25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H26" s="5"/>
+      <c r="I26" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
@@ -2277,39 +2293,42 @@
         <v>37</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H27" s="5"/>
+      <c r="I27" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J27" t="s">
+        <v>227</v>
+      </c>
+      <c r="K27" t="s">
         <v>228</v>
-      </c>
-      <c r="K27" t="s">
-        <v>229</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
@@ -2318,29 +2337,29 @@
         <v>37</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="5"/>
@@ -2358,16 +2377,16 @@
         <v>46</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P28" t="s">
         <v>29</v>
       </c>
       <c r="Q28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S28" t="s">
         <v>42</v>
@@ -2375,20 +2394,20 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>187</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>188</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="5"/>
@@ -2406,10 +2425,10 @@
         <v>46</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P29" t="s">
         <v>29</v>
@@ -2423,21 +2442,21 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H30" s="5"/>
       <c r="J30">
@@ -2448,10 +2467,10 @@
         <v>36</v>
       </c>
       <c r="L30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P30" t="s">
         <v>61</v>
@@ -2462,21 +2481,21 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H31" s="5"/>
       <c r="J31">
@@ -2487,10 +2506,10 @@
         <v>36</v>
       </c>
       <c r="L31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P31" t="s">
         <v>61</v>
@@ -2501,18 +2520,18 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="5"/>
@@ -2524,10 +2543,10 @@
         <v>36</v>
       </c>
       <c r="L32" t="s">
+        <v>98</v>
+      </c>
+      <c r="O32" t="s">
         <v>99</v>
-      </c>
-      <c r="O32" t="s">
-        <v>100</v>
       </c>
       <c r="S32" t="s">
         <v>20</v>
@@ -2535,18 +2554,18 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="5"/>
@@ -2555,13 +2574,13 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S33" t="s">
         <v>42</v>
@@ -2569,97 +2588,97 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" t="s">
         <v>105</v>
-      </c>
-      <c r="B44" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" t="s">
         <v>107</v>
-      </c>
-      <c r="B45" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" t="s">
         <v>109</v>
-      </c>
-      <c r="B46" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" t="s">
         <v>111</v>
-      </c>
-      <c r="B47" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" t="s">
         <v>113</v>
-      </c>
-      <c r="B48" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" t="s">
         <v>115</v>
-      </c>
-      <c r="B49" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" t="s">
         <v>117</v>
-      </c>
-      <c r="B50" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" t="s">
         <v>119</v>
-      </c>
-      <c r="B51" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" t="s">
         <v>121</v>
-      </c>
-      <c r="B52" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2951,6 +2970,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -2959,15 +2987,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2990,26 +3009,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="287" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7CCB523-DD9C-2142-9C4D-294B5C6C4BAA}"/>
+  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0779C6BC-9F46-FE46-B9B1-D42CCBE321FE}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="760" windowWidth="30660" windowHeight="15420" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="280" yWindow="760" windowWidth="33820" windowHeight="19080" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="231">
   <si>
     <t>Publication CodeName</t>
   </si>
@@ -724,9 +724,6 @@
   </si>
   <si>
     <t>docx online</t>
-  </si>
-  <si>
-    <t>units</t>
   </si>
   <si>
     <t>JardimMesseder_etal_2017_Table1.csv</t>
@@ -791,12 +788,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -812,7 +815,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -827,7 +830,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1505,92 +1513,92 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S8" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" t="s">
+      <c r="E9" s="13"/>
+      <c r="F9" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="5" t="s">
+      <c r="G9" s="14"/>
+      <c r="H9" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="S9" t="s">
+      <c r="S9" s="12" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1757,319 +1765,319 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" t="s">
+      <c r="E14" s="13"/>
+      <c r="F14" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S14" t="s">
+      <c r="S14" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" t="s">
+      <c r="E15" s="13"/>
+      <c r="F15" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S15" t="s">
+      <c r="S15" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" t="s">
+      <c r="E16" s="13"/>
+      <c r="F16" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="N16" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S16" t="s">
+      <c r="S16" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" t="s">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N17" s="3" t="s">
+      <c r="N17" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S17" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" t="s">
+      <c r="E18" s="13"/>
+      <c r="F18" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="N18" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="O18" t="s">
+      <c r="O18" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S18" t="s">
+      <c r="S18" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" t="s">
+      <c r="E19" s="13"/>
+      <c r="F19" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="O19" t="s">
+      <c r="O19" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="S19" t="s">
+      <c r="S19" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:19" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="13"/>
+      <c r="D20" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" t="s">
+      <c r="E20" s="13"/>
+      <c r="F20" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="O20" t="s">
+      <c r="O20" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S20" s="12" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2217,132 +2225,132 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" t="s">
+      <c r="E25" s="13"/>
+      <c r="F25" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="I25" s="7" t="s">
+      <c r="G25" s="14"/>
+      <c r="H25" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="I25" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J25" t="s">
-        <v>230</v>
-      </c>
-      <c r="K25" t="s">
+      <c r="J25" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="K25" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M25" t="s">
+      <c r="M25" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O25" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S25" t="s">
+      <c r="S25" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7" t="s">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="F26" t="s">
-        <v>229</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="E26" s="13"/>
+      <c r="F26" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="G26" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="7" t="s">
+      <c r="H26" s="15"/>
+      <c r="I26" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="N26" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="O26" t="s">
+      <c r="O26" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="S26" t="s">
+      <c r="S26" s="12" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7" t="s">
+      <c r="C27" s="13"/>
+      <c r="D27" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="F27" t="s">
-        <v>229</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="E27" s="13"/>
+      <c r="F27" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="G27" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="7" t="s">
+      <c r="H27" s="15"/>
+      <c r="I27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L27" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M27" t="s">
+      <c r="M27" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="N27" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O27" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="S27" t="s">
+      <c r="S27" s="12" t="s">
         <v>178</v>
       </c>
     </row>

--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0779C6BC-9F46-FE46-B9B1-D42CCBE321FE}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8621A9CB-C081-5C4A-B469-5BAD279D947B}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="760" windowWidth="33820" windowHeight="19080" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
@@ -1156,14 +1156,14 @@
   <cols>
     <col min="1" max="1" width="24.1640625" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" customWidth="1"/>
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" customWidth="1"/>
-    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="10" max="10" width="35.33203125" customWidth="1"/>
     <col min="11" max="11" width="13.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="22.1640625" customWidth="1"/>
@@ -2978,15 +2978,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -2995,6 +2986,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3017,26 +3017,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/__READ ME.xlsx
+++ b/__READ ME.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33F50087-34D4-404E-A2D7-BF440F60F475}"/>
+  <xr:revisionPtr revIDLastSave="532" documentId="13_ncr:1_{A611BB1F-8283-7640-98A2-533433C96266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06731EDA-33C8-8B47-8AC2-21C6163D5261}"/>
   <bookViews>
-    <workbookView xWindow="34880" yWindow="-5960" windowWidth="49880" windowHeight="22660" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView minimized="1" xWindow="34560" yWindow="-6580" windowWidth="37960" windowHeight="20180" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="254">
   <si>
     <t>Publication CodeName</t>
   </si>
@@ -67,9 +66,6 @@
   </si>
   <si>
     <t>Main Trait(s)</t>
-  </si>
-  <si>
-    <t>Kind of data</t>
   </si>
   <si>
     <t>Possible Traits</t>
@@ -673,9 +669,6 @@
     <t>1st Author (no punctuation)</t>
   </si>
   <si>
-    <t>unpublished</t>
-  </si>
-  <si>
     <t>year</t>
   </si>
   <si>
@@ -685,9 +678,6 @@
     <t>sequence</t>
   </si>
   <si>
-    <t>ENCODED</t>
-  </si>
-  <si>
     <t>I</t>
   </si>
   <si>
@@ -800,6 +790,15 @@
   </si>
   <si>
     <t>2013</t>
+  </si>
+  <si>
+    <t>Item comparative-data (tsv) encoded</t>
+  </si>
+  <si>
+    <t>Item name</t>
+  </si>
+  <si>
+    <t>Source type</t>
   </si>
 </sst>
 </file>
@@ -1228,16 +1227,15 @@
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="12.1640625" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="31.6640625" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="23.33203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="46.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.1640625" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="10" width="46.83203125" customWidth="1"/>
     <col min="11" max="11" width="23.1640625" customWidth="1"/>
     <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="13" max="13" width="41.1640625" customWidth="1"/>
+    <col min="14" max="14" width="53.5" customWidth="1"/>
     <col min="15" max="15" width="5.33203125" customWidth="1"/>
     <col min="16" max="16" width="35.33203125" customWidth="1"/>
     <col min="17" max="17" width="13.83203125" customWidth="1"/>
@@ -1254,31 +1252,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>252</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -1293,7 +1294,7 @@
         <v>4</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>5</v>
@@ -1311,16 +1312,16 @@
         <v>9</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
@@ -1329,1744 +1330,1745 @@
         <v>_Unpublished_ProjectKaskan</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="7" t="s">
-        <v>211</v>
-      </c>
+      <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="I2" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A2,(SUBSTITUTE(H2," ",""))))</f>
+        <v>_Unpublished_ProjectKaskan_</v>
+      </c>
       <c r="J2" s="7" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A2,(SUBSTITUTE(I2," ",""))))</f>
-        <v>_Unpublished_ProjectKaskan_</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F2, H2), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>_</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="Q2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" t="s">
         <v>15</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>16</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>17</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>18</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="str">
-        <f>B3 &amp; IF(C3&lt;&gt;"", "_" &amp; C3, "") &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "") &amp; IF(E3&lt;&gt;"", "-" &amp; E3, "")</f>
+        <f t="shared" ref="A3:A29" si="0">B3 &amp; IF(C3&lt;&gt;"", "_" &amp; C3, "") &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "") &amp; IF(E3&lt;&gt;"", "-" &amp; E3, "")</f>
         <v>Burger_etal_2019</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G3" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(F3, "/", "%2F"), ":", "%3A")</f>
-        <v>10.1093%2Fjmammal%2Fgyz043</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7" t="s">
-        <v>116</v>
+      <c r="I3" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A3,(SUBSTITUTE(H3," ",""))))</f>
+        <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="J3" s="7" t="str">
-        <f t="shared" ref="J3:J33" si="0">TRIM(_xlfn.TEXTJOIN("_",FALSE,A3,(SUBSTITUTE(I3," ",""))))</f>
-        <v>Burger_etal_2019_SupplementaryDataSD1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F3, H3), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" t="s">
         <v>21</v>
-      </c>
-      <c r="O3" t="s">
-        <v>22</v>
       </c>
       <c r="P3" t="str">
         <f>IF(O3="N", N3, O3)</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
       <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
         <v>23</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>24</v>
       </c>
-      <c r="S3" t="s">
+      <c r="U3" t="s">
         <v>25</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>26</v>
       </c>
-      <c r="V3" t="s">
+      <c r="X3" t="s">
         <v>27</v>
       </c>
-      <c r="X3" t="s">
-        <v>28</v>
-      </c>
       <c r="Y3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="str">
-        <f>B4 &amp; IF(C4&lt;&gt;"", "_" &amp; C4, "") &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "") &amp; IF(E4&lt;&gt;"", "-" &amp; E4, "")</f>
+        <f t="shared" si="0"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G33" si="1">SUBSTITUTE(SUBSTITUTE(F4, "/", "%2F"), ":", "%3A")</f>
-        <v>10.7554%2FeLife.77875</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7" t="s">
-        <v>112</v>
+      <c r="I4" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A4,(SUBSTITUTE(H4," ",""))))</f>
+        <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="J4" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Caspar_etal_2022_Table1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F4, H4), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
         <v>29</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>30</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>31</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
         <v>33</v>
       </c>
-      <c r="R4" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="T4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="U4" t="s">
         <v>35</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>36</v>
       </c>
-      <c r="V4" t="s">
+      <c r="X4" t="s">
         <v>37</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>38</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="str">
-        <f>B5 &amp; IF(C5&lt;&gt;"", "_" &amp; C5, "") &amp; IF(D5&lt;&gt;"", "_" &amp; D5, "") &amp; IF(E5&lt;&gt;"", "-" &amp; E5, "")</f>
+        <f t="shared" si="0"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.7554%2FeLife.77875</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A5,(SUBSTITUTE(H5," ",""))))</f>
+        <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="J5" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Caspar_etal_2022_Supplementaryfile3</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F5, H5), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
         <v>40</v>
       </c>
-      <c r="N5" t="s">
-        <v>41</v>
-      </c>
       <c r="O5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5" t="str">
         <f>IF(O5="Y", O5, N5)</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
       <c r="Q5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
         <v>42</v>
       </c>
-      <c r="R5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="T5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="U5" t="s">
         <v>44</v>
       </c>
-      <c r="U5" t="s">
-        <v>45</v>
-      </c>
       <c r="V5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="str">
-        <f>B6 &amp; IF(C6&lt;&gt;"", "_" &amp; C6, "") &amp; IF(D6&lt;&gt;"", "_" &amp; D6, "") &amp; IF(E6&lt;&gt;"", "-" &amp; E6, "")</f>
+        <f t="shared" si="0"/>
         <v>Changizi_etal_2001</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1007%2Fs004220000205</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9" t="s">
-        <v>120</v>
+      <c r="I6" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A6,(SUBSTITUTE(H6," ",""))))</f>
+        <v>Changizi_etal_2001_Figure3</v>
       </c>
       <c r="J6" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Changizi_etal_2001_Figure3</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F6, H6), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P6" t="str">
-        <f t="shared" ref="P6:P33" si="2">IF(O6="Y", O6, N6)</f>
+        <f t="shared" ref="P6:P33" si="1">IF(O6="Y", O6, N6)</f>
         <v>Y</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T6" s="6"/>
       <c r="U6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="X6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="str">
-        <f>B7 &amp; IF(C7&lt;&gt;"", "_" &amp; C7, "") &amp; IF(D7&lt;&gt;"", "_" &amp; D7, "") &amp; IF(E7&lt;&gt;"", "-" &amp; E7, "")</f>
+        <f t="shared" si="0"/>
         <v>Chen_Wiens_2020</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1038%2Fs41467-020-14356-3</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
-        <v>122</v>
+      <c r="I7" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A7,(SUBSTITUTE(H7," ",""))))</f>
+        <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
       <c r="J7" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Chen_Wiens_2020_SupplementaryData3</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F7, H7), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="1"/>
+        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>41</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>42</v>
+      </c>
+      <c r="T7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="O7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" t="str">
-        <f t="shared" si="2"/>
-        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" t="s">
-        <v>43</v>
-      </c>
-      <c r="T7" s="3" t="s">
+      <c r="U7" t="s">
         <v>47</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
+        <v>26</v>
+      </c>
+      <c r="W7" t="s">
         <v>48</v>
       </c>
-      <c r="V7" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y7" t="s">
         <v>49</v>
-      </c>
-      <c r="X7" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="str">
-        <f>B8 &amp; IF(C8&lt;&gt;"", "_" &amp; C8, "") &amp; IF(D8&lt;&gt;"", "_" &amp; D8, "") &amp; IF(E8&lt;&gt;"", "-" &amp; E8, "")</f>
+        <f t="shared" si="0"/>
         <v>DosSantos_etal_2017</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F8" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000452856</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A8,(SUBSTITUTE(H8," ",""))))</f>
+        <v>DosSantos_etal_2017_TableS1</v>
+      </c>
+      <c r="J8" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F8, H8), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000452856_TableS1</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="J8" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>DosSantos_etal_2017_TableS1</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>125</v>
-      </c>
       <c r="L8" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q8" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q8" s="12" t="s">
+      <c r="R8" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R8" s="12" t="s">
+      <c r="S8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="T8" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="S8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="T8" s="14" t="s">
+      <c r="U8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="U8" s="12" t="s">
+      <c r="V8" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="V8" s="12" t="s">
+      <c r="Y8" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="Y8" s="12" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="str">
-        <f>B9 &amp; IF(C9&lt;&gt;"", "_" &amp; C9, "") &amp; IF(D9&lt;&gt;"", "_" &amp; D9, "") &amp; IF(E9&lt;&gt;"", "-" &amp; E9, "")</f>
+        <f t="shared" si="0"/>
         <v>DosSantos_etal_2020</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A9,(SUBSTITUTE(H9," ",""))))</f>
+        <v>DosSantos_etal_2020_Table1</v>
       </c>
       <c r="J9" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>DosSantos_etal_2020_Table1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F9, H9), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
       <c r="K9" s="13"/>
       <c r="L9" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M9" s="14"/>
       <c r="N9" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="O9" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>196</v>
-      </c>
       <c r="Q9" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R9" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="V9" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="V9" s="12" t="s">
-        <v>56</v>
-      </c>
       <c r="Y9" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="str">
-        <f>B10 &amp; IF(C10&lt;&gt;"", "_" &amp; C10, "") &amp; IF(D10&lt;&gt;"", "_" &amp; D10, "") &amp; IF(E10&lt;&gt;"", "-" &amp; E10, "")</f>
+        <f t="shared" si="0"/>
         <v>Finlay_etal_2006</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G10" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> none - find ISBN</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7" t="s">
-        <v>131</v>
+        <v>176</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I10" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A10,(SUBSTITUTE(H10," ",""))))</f>
+        <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="J10" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Finlay_etal_2006_Table6.1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F10, H10), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>none-findISBN_Table6.1</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="Q10" t="s">
         <v>59</v>
       </c>
-      <c r="O10" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" t="s">
+        <v>33</v>
+      </c>
+      <c r="T10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="R10" t="s">
-        <v>24</v>
-      </c>
-      <c r="S10" t="s">
-        <v>34</v>
-      </c>
-      <c r="T10" s="3" t="s">
+      <c r="U10" t="s">
+        <v>193</v>
+      </c>
+      <c r="X10" t="s">
         <v>61</v>
       </c>
-      <c r="U10" t="s">
-        <v>194</v>
-      </c>
-      <c r="X10" t="s">
-        <v>62</v>
-      </c>
       <c r="Y10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="str">
-        <f>B11 &amp; IF(C11&lt;&gt;"", "_" &amp; C11, "") &amp; IF(D11&lt;&gt;"", "_" &amp; D11, "") &amp; IF(E11&lt;&gt;"", "-" &amp; E11, "")</f>
+        <f t="shared" si="0"/>
         <v>Heffner_Masterton_1975</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000124401</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A11,(SUBSTITUTE(H11," ",""))))</f>
+        <v>Heffner_Masterton_1975_TableI</v>
       </c>
       <c r="J11" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Heffner_Masterton_1975_TableI</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F11, H11), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" t="s">
+        <v>180</v>
+      </c>
+      <c r="O11" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" t="s">
+        <v>107</v>
+      </c>
+      <c r="U11" t="s">
+        <v>63</v>
+      </c>
+      <c r="V11" t="s">
         <v>181</v>
       </c>
-      <c r="O11" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>33</v>
-      </c>
-      <c r="R11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S11" t="s">
-        <v>108</v>
-      </c>
-      <c r="U11" t="s">
+      <c r="W11" t="s">
         <v>64</v>
       </c>
-      <c r="V11" t="s">
-        <v>182</v>
-      </c>
-      <c r="W11" t="s">
-        <v>65</v>
-      </c>
       <c r="Y11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="str">
-        <f>B12 &amp; IF(C12&lt;&gt;"", "_" &amp; C12, "") &amp; IF(D12&lt;&gt;"", "_" &amp; D12, "") &amp; IF(E12&lt;&gt;"", "-" &amp; E12, "")</f>
+        <f t="shared" si="0"/>
         <v>Heffner_Masterton_1983</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G12" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000121494</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I12" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A12,(SUBSTITUTE(H12," ",""))))</f>
+        <v>Heffner_Masterton_1983_TableI</v>
       </c>
       <c r="J12" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Heffner_Masterton_1983_TableI</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F12, H12), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000121494_TableI</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="5"/>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="str">
-        <f>B13 &amp; IF(C13&lt;&gt;"", "_" &amp; C13, "") &amp; IF(D13&lt;&gt;"", "_" &amp; D13, "") &amp; IF(E13&lt;&gt;"", "-" &amp; E13, "")</f>
+        <f t="shared" si="0"/>
         <v>Heldstab_etal_2016</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G13" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1038%2Fsrep24528</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I13" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A13,(SUBSTITUTE(H13," ",""))))</f>
+        <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="J13" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Heldstab_etal_2016_TableS1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F13, H13), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="5"/>
       <c r="P13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
+        <v>23</v>
+      </c>
+      <c r="U13" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A14,(SUBSTITUTE(H14," ",""))))</f>
+        <v>HerculanoHouzel_etal_2015_Table1</v>
+      </c>
+      <c r="J14" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F14, H14), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000437413_Table1</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y14" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A15,(SUBSTITUTE(H15," ",""))))</f>
+        <v>HerculanoHouzel_etal_2015_Table2</v>
+      </c>
+      <c r="J15" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F15, H15), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000437413_Table2</v>
+      </c>
+      <c r="K15" s="13"/>
+      <c r="L15" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y15" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A16,(SUBSTITUTE(H16," ",""))))</f>
+        <v>HerculanoHouzel_etal_2015_Table3</v>
+      </c>
+      <c r="J16" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F16, H16), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000437413_Table3</v>
+      </c>
+      <c r="K16" s="13"/>
+      <c r="L16" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y16" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A17,(SUBSTITUTE(H17," ",""))))</f>
+        <v>HerculanoHouzel_etal_2015_Table4</v>
+      </c>
+      <c r="J17" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F17, H17), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000437413_Table4</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y17" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A18,(SUBSTITUTE(H18," ",""))))</f>
+        <v>HerculanoHouzel_etal_2015_Table5</v>
+      </c>
+      <c r="J18" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F18, H18), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000437413_Table5</v>
+      </c>
+      <c r="K18" s="13"/>
+      <c r="L18" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T18" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="U18" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y18" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A19,(SUBSTITUTE(H19," ",""))))</f>
+        <v>HerculanoHouzel_etal_2020_TABLE1</v>
+      </c>
+      <c r="J19" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F19, H19), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1002%2Fcne.24985_TABLE1</v>
+      </c>
+      <c r="K19" s="13"/>
+      <c r="L19" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S19" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y19" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A20,(SUBSTITUTE(H20," ",""))))</f>
+        <v>HerculanoHouzel_etal_2020_TABLE2</v>
+      </c>
+      <c r="J20" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F20, H20), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1002%2Fcne.24985_TABLE2</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S20" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="U20" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y20" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Iwaniuk_etal_2016</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A21,(SUBSTITUTE(H21," ",""))))</f>
+        <v>Iwaniuk_etal_2016_Table1</v>
+      </c>
+      <c r="J21" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F21, H21), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="N21" s="5"/>
+      <c r="P21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" t="s">
+        <v>23</v>
+      </c>
+      <c r="U21" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Iwaniuk_etal_2016</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A22,(SUBSTITUTE(H22," ",""))))</f>
+        <v>Iwaniuk_etal_2016_Table2</v>
+      </c>
+      <c r="J22" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F22, H22), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="P22">
+        <f t="shared" ref="P22:P23" si="2">IF(O22="Y", O22, N22)</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>23</v>
+      </c>
+      <c r="U22" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Iwaniuk_etal_2016</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A23,(SUBSTITUTE(H23," ",""))))</f>
+        <v>Iwaniuk_etal_2016_Table3</v>
+      </c>
+      <c r="J23" s="7" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F23, H23), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" t="s">
+        <v>62</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="N23" s="5"/>
+      <c r="P23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q13" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" t="s">
-        <v>24</v>
-      </c>
-      <c r="U13" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="str">
-        <f>B14 &amp; IF(C14&lt;&gt;"", "_" &amp; C14, "") &amp; IF(D14&lt;&gt;"", "_" &amp; D14, "") &amp; IF(E14&lt;&gt;"", "-" &amp; E14, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G14" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000437413</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HerculanoHouzel_etal_2015_Table1</v>
-      </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T14" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U14" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y14" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="str">
-        <f>B15 &amp; IF(C15&lt;&gt;"", "_" &amp; C15, "") &amp; IF(D15&lt;&gt;"", "_" &amp; D15, "") &amp; IF(E15&lt;&gt;"", "-" &amp; E15, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G15" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000437413</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="J15" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HerculanoHouzel_etal_2015_Table2</v>
-      </c>
-      <c r="K15" s="13"/>
-      <c r="L15" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="N15" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T15" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y15" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="str">
-        <f>B16 &amp; IF(C16&lt;&gt;"", "_" &amp; C16, "") &amp; IF(D16&lt;&gt;"", "_" &amp; D16, "") &amp; IF(E16&lt;&gt;"", "-" &amp; E16, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G16" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000437413</v>
-      </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="J16" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HerculanoHouzel_etal_2015_Table3</v>
-      </c>
-      <c r="K16" s="13"/>
-      <c r="L16" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S16" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T16" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y16" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="str">
-        <f>B17 &amp; IF(C17&lt;&gt;"", "_" &amp; C17, "") &amp; IF(D17&lt;&gt;"", "_" &amp; D17, "") &amp; IF(E17&lt;&gt;"", "-" &amp; E17, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000437413</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="J17" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HerculanoHouzel_etal_2015_Table4</v>
-      </c>
-      <c r="K17" s="13"/>
-      <c r="L17" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="M17" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T17" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y17" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="str">
-        <f>B18 &amp; IF(C18&lt;&gt;"", "_" &amp; C18, "") &amp; IF(D18&lt;&gt;"", "_" &amp; D18, "") &amp; IF(E18&lt;&gt;"", "-" &amp; E18, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G18" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000437413</v>
-      </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="J18" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HerculanoHouzel_etal_2015_Table5</v>
-      </c>
-      <c r="K18" s="13"/>
-      <c r="L18" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="M18" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="N18" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S18" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T18" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y18" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="str">
-        <f>B19 &amp; IF(C19&lt;&gt;"", "_" &amp; C19, "") &amp; IF(D19&lt;&gt;"", "_" &amp; D19, "") &amp; IF(E19&lt;&gt;"", "-" &amp; E19, "")</f>
-        <v>HerculanoHouzel_etal_2020</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G19" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1002%2Fcne.24985</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J19" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HerculanoHouzel_etal_2020_TABLE1</v>
-      </c>
-      <c r="K19" s="13"/>
-      <c r="L19" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="M19" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="N19" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R19" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S19" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y19" s="12" t="s">
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" t="s">
+        <v>23</v>
+      </c>
+      <c r="U23" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:25" s="12" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="str">
-        <f>B20 &amp; IF(C20&lt;&gt;"", "_" &amp; C20, "") &amp; IF(D20&lt;&gt;"", "_" &amp; D20, "") &amp; IF(E20&lt;&gt;"", "-" &amp; E20, "")</f>
-        <v>HerculanoHouzel_etal_2020</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G20" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1002%2Fcne.24985</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="J20" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>HerculanoHouzel_etal_2020_TABLE2</v>
-      </c>
-      <c r="K20" s="13"/>
-      <c r="L20" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="M20" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="N20" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S20" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y20" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="str">
-        <f>B21 &amp; IF(C21&lt;&gt;"", "_" &amp; C21, "") &amp; IF(D21&lt;&gt;"", "_" &amp; D21, "") &amp; IF(E21&lt;&gt;"", "-" &amp; E21, "")</f>
-        <v>Iwaniuk_etal_2016</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G21" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1037%2F0735-7036.115.1.29</v>
-      </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="J21" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Iwaniuk_etal_2016_Table1</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" t="s">
-        <v>63</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="N21" s="5"/>
-      <c r="P21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>33</v>
-      </c>
-      <c r="R21" t="s">
-        <v>24</v>
-      </c>
-      <c r="U21" t="s">
+      <c r="Y23" t="s">
         <v>71</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="str">
-        <f>B22 &amp; IF(C22&lt;&gt;"", "_" &amp; C22, "") &amp; IF(D22&lt;&gt;"", "_" &amp; D22, "") &amp; IF(E22&lt;&gt;"", "-" &amp; E22, "")</f>
-        <v>Iwaniuk_etal_2016</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1037%2F0735-7036.115.1.29</v>
-      </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="J22" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Iwaniuk_etal_2016_Table2</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" t="s">
-        <v>63</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="N22" s="5"/>
-      <c r="P22">
-        <f t="shared" ref="P22:P23" si="3">IF(O22="Y", O22, N22)</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>33</v>
-      </c>
-      <c r="R22" t="s">
-        <v>24</v>
-      </c>
-      <c r="U22" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="str">
-        <f>B23 &amp; IF(C23&lt;&gt;"", "_" &amp; C23, "") &amp; IF(D23&lt;&gt;"", "_" &amp; D23, "") &amp; IF(E23&lt;&gt;"", "-" &amp; E23, "")</f>
-        <v>Iwaniuk_etal_2016</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G23" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1037%2F0735-7036.115.1.29</v>
-      </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="J23" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Iwaniuk_etal_2016_Table3</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" t="s">
-        <v>63</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="N23" s="5"/>
-      <c r="P23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>33</v>
-      </c>
-      <c r="R23" t="s">
-        <v>24</v>
-      </c>
-      <c r="U23" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="str">
-        <f>B24 &amp; IF(C24&lt;&gt;"", "_" &amp; C24, "") &amp; IF(D24&lt;&gt;"", "_" &amp; D24, "") &amp; IF(E24&lt;&gt;"", "-" &amp; E24, "")</f>
+        <f t="shared" si="0"/>
         <v>Iwaniuk_etal_2016</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1037%2F0735-7036.115.1.29</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7" t="s">
-        <v>135</v>
+        <v>148</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I24" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A24,(SUBSTITUTE(H24," ",""))))</f>
+        <v>Iwaniuk_etal_2016_Table4</v>
       </c>
       <c r="J24" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Iwaniuk_etal_2016_Table4</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F24, H24), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N24" s="5"/>
       <c r="P24">
-        <f t="shared" ref="P24" si="4">IF(O24="Y", O24, N24)</f>
+        <f t="shared" ref="P24" si="3">IF(O24="Y", O24, N24)</f>
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U24" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y24" t="s">
         <v>71</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="str">
-        <f>B25 &amp; IF(C25&lt;&gt;"", "_" &amp; C25, "") &amp; IF(D25&lt;&gt;"", "_" &amp; D25, "") &amp; IF(E25&lt;&gt;"", "-" &amp; E25, "")</f>
+        <f t="shared" si="0"/>
         <v>JardimMesseder_etal_2017</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="G25" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.3389%2Ffnana.2017.00118</v>
-      </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13" t="s">
-        <v>112</v>
+        <v>153</v>
+      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A25,(SUBSTITUTE(H25," ",""))))</f>
+        <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="J25" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>JardimMesseder_etal_2017_Table1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F25, H25), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M25" s="14"/>
       <c r="N25" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S25" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="R25" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S25" s="12" t="s">
-        <v>34</v>
-      </c>
       <c r="U25" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y25" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="str">
-        <f>B26 &amp; IF(C26&lt;&gt;"", "_" &amp; C26, "") &amp; IF(D26&lt;&gt;"", "_" &amp; D26, "") &amp; IF(E26&lt;&gt;"", "-" &amp; E26, "")</f>
+        <f t="shared" si="0"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G26" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1038%2Fs41598-018-26062-8</v>
-      </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13" t="s">
-        <v>124</v>
+        <v>154</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A26,(SUBSTITUTE(H26," ",""))))</f>
+        <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="J26" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Kverkova_etal_2018_TableS1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F26, H26), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="K26" s="13"/>
       <c r="L26" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M26" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N26" s="15"/>
       <c r="O26" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q26" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="R26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T26" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="R26" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S26" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T26" s="14" t="s">
-        <v>204</v>
-      </c>
       <c r="U26" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y26" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="str">
-        <f>B27 &amp; IF(C27&lt;&gt;"", "_" &amp; C27, "") &amp; IF(D27&lt;&gt;"", "_" &amp; D27, "") &amp; IF(E27&lt;&gt;"", "-" &amp; E27, "")</f>
+        <f t="shared" si="0"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="G27" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1038%2Fs41598-018-26062-8</v>
-      </c>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13" t="s">
-        <v>156</v>
+      <c r="I27" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A27,(SUBSTITUTE(H27," ",""))))</f>
+        <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="J27" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Kverkova_etal_2018_TableS5</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F27, H27), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="K27" s="13"/>
       <c r="L27" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N27" s="15"/>
       <c r="O27" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P27" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q27" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="Q27" s="12" t="s">
-        <v>207</v>
-      </c>
       <c r="R27" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y27" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="str">
-        <f>B28 &amp; IF(C28&lt;&gt;"", "_" &amp; C28, "") &amp; IF(D28&lt;&gt;"", "_" &amp; D28, "") &amp; IF(E28&lt;&gt;"", "-" &amp; E28, "")</f>
+        <f t="shared" si="0"/>
         <v>ManyPrimates_etal_2022</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G28" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.26451%2Fabc.09.04.06.2022</v>
-      </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A28,(SUBSTITUTE(H28," ",""))))</f>
+        <v>ManyPrimates_etal_2022_data/species_predictors.xlsx</v>
       </c>
       <c r="J28" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>ManyPrimates_etal_2022_data/species_predictors.xlsx</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F28, H28), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspecies_predictors.xlsx</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="5"/>
       <c r="P28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q28" t="s">
+        <v>41</v>
+      </c>
+      <c r="R28" t="s">
+        <v>23</v>
+      </c>
+      <c r="S28" t="s">
         <v>42</v>
       </c>
-      <c r="R28" t="s">
-        <v>24</v>
-      </c>
-      <c r="S28" t="s">
-        <v>43</v>
-      </c>
       <c r="T28" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U28" t="s">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s">
+        <v>26</v>
+      </c>
+      <c r="W28" t="s">
         <v>75</v>
       </c>
-      <c r="V28" t="s">
-        <v>27</v>
-      </c>
-      <c r="W28" t="s">
-        <v>76</v>
-      </c>
       <c r="Y28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="str">
-        <f>B29 &amp; IF(C29&lt;&gt;"", "_" &amp; C29, "") &amp; IF(D29&lt;&gt;"", "_" &amp; D29, "") &amp; IF(E29&lt;&gt;"", "-" &amp; E29, "")</f>
+        <f t="shared" si="0"/>
         <v>Powell_etal_2017</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="G29" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>166</v>
+      <c r="I29" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A29,(SUBSTITUTE(H29," ",""))))</f>
+        <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="J29" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F29, H29), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M29" s="3"/>
       <c r="N29" s="5"/>
       <c r="P29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q29" t="s">
+        <v>41</v>
+      </c>
+      <c r="R29" t="s">
+        <v>23</v>
+      </c>
+      <c r="S29" t="s">
         <v>42</v>
       </c>
-      <c r="R29" t="s">
-        <v>24</v>
-      </c>
-      <c r="S29" t="s">
-        <v>43</v>
-      </c>
       <c r="T29" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.2">
@@ -3075,58 +3077,58 @@
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D30" s="3">
         <v>2004</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G30" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000075672</v>
-      </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7" t="s">
-        <v>135</v>
+        <v>167</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A30,(SUBSTITUTE(H30," ",""))))</f>
+        <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="J30" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Sherwood_etal_2004_I_Table4</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F30, H30), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N30" s="5"/>
       <c r="P30">
-        <f t="shared" ref="P30" si="5">IF(O30="Y", O30, N30)</f>
+        <f t="shared" ref="P30" si="4">IF(O30="Y", O30, N30)</f>
         <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.2">
@@ -3135,58 +3137,58 @@
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D31" s="3">
         <v>2004</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G31" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1159%2F000075672</v>
-      </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7" t="s">
-        <v>136</v>
+        <v>167</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I31" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A31,(SUBSTITUTE(H31," ",""))))</f>
+        <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="J31" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F31, H31), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N31" s="5"/>
       <c r="P31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.2">
@@ -3195,51 +3197,51 @@
         <v>Winkler_Bryant_2021</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="G32" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.1080%2F09524622.2021.1905065</v>
-      </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7" t="s">
-        <v>172</v>
+      <c r="I32" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A32,(SUBSTITUTE(H32," ",""))))</f>
+        <v>Winkler_Bryant_2021_Figure1</v>
       </c>
       <c r="J32" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F32, H32), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="5"/>
       <c r="P32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R32" t="s">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s">
         <v>79</v>
       </c>
-      <c r="U32" t="s">
-        <v>80</v>
-      </c>
       <c r="Y32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.2">
@@ -3248,186 +3250,186 @@
         <v>Young_etal_2013</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="G33" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.3389%2Ffncir.2013.00030</v>
-      </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7" t="s">
-        <v>112</v>
+        <v>172</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I33" s="7" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A33,(SUBSTITUTE(H33," ",""))))</f>
+        <v>Young_etal_2013_Table1</v>
       </c>
       <c r="J33" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Young_etal_2013_Table1</v>
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F33, H33), "/", "%2F"), ":", "%3A"), " ", ""))</f>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="5"/>
       <c r="P33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3449,699 +3451,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F29001C-6C99-054C-B702-FDED8218255F}">
-  <dimension ref="B2:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="G2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="G3" t="s">
-        <v>220</v>
-      </c>
-      <c r="H3" t="s">
-        <v>221</v>
-      </c>
-      <c r="I3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="G4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H4" t="s">
-        <v>221</v>
-      </c>
-      <c r="I4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="G5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H5" t="s">
-        <v>221</v>
-      </c>
-      <c r="I5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="G6" t="s">
-        <v>225</v>
-      </c>
-      <c r="H6" t="s">
-        <v>221</v>
-      </c>
-      <c r="I6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="G7" t="s">
-        <v>227</v>
-      </c>
-      <c r="H7" t="s">
-        <v>228</v>
-      </c>
-      <c r="I7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="G8" t="s">
-        <v>230</v>
-      </c>
-      <c r="H8" t="s">
-        <v>221</v>
-      </c>
-      <c r="I8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="G9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H9" t="s">
-        <v>221</v>
-      </c>
-      <c r="I9" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="G10" t="s">
-        <v>232</v>
-      </c>
-      <c r="H10" t="s">
-        <v>221</v>
-      </c>
-      <c r="I10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="G11" t="s">
-        <v>234</v>
-      </c>
-      <c r="H11" t="s">
-        <v>235</v>
-      </c>
-      <c r="I11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="G12" t="s">
-        <v>234</v>
-      </c>
-      <c r="H12" t="s">
-        <v>235</v>
-      </c>
-      <c r="I12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="G13" t="s">
-        <v>238</v>
-      </c>
-      <c r="H13" t="s">
-        <v>221</v>
-      </c>
-      <c r="I13" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="G14" t="s">
-        <v>240</v>
-      </c>
-      <c r="H14" t="s">
-        <v>221</v>
-      </c>
-      <c r="I14" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E15" s="14"/>
-      <c r="G15" t="s">
-        <v>240</v>
-      </c>
-      <c r="H15" t="s">
-        <v>221</v>
-      </c>
-      <c r="I15" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B16" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E16" s="14"/>
-      <c r="G16" t="s">
-        <v>240</v>
-      </c>
-      <c r="H16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I16" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E17" s="14"/>
-      <c r="G17" t="s">
-        <v>240</v>
-      </c>
-      <c r="H17" t="s">
-        <v>221</v>
-      </c>
-      <c r="I17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E18" s="14"/>
-      <c r="G18" t="s">
-        <v>240</v>
-      </c>
-      <c r="H18" t="s">
-        <v>221</v>
-      </c>
-      <c r="I18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E19" s="14"/>
-      <c r="G19" t="s">
-        <v>240</v>
-      </c>
-      <c r="H19" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E20" s="14"/>
-      <c r="G20" t="s">
-        <v>240</v>
-      </c>
-      <c r="H20" t="s">
-        <v>221</v>
-      </c>
-      <c r="I20" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="G21" t="s">
-        <v>242</v>
-      </c>
-      <c r="H21" t="s">
-        <v>221</v>
-      </c>
-      <c r="I21" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="G22" t="s">
-        <v>242</v>
-      </c>
-      <c r="H22" t="s">
-        <v>221</v>
-      </c>
-      <c r="I22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B23" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="G23" t="s">
-        <v>242</v>
-      </c>
-      <c r="H23" t="s">
-        <v>221</v>
-      </c>
-      <c r="I23" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B24" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="G24" t="s">
-        <v>242</v>
-      </c>
-      <c r="H24" t="s">
-        <v>221</v>
-      </c>
-      <c r="I24" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E25" s="14"/>
-      <c r="G25" t="s">
-        <v>243</v>
-      </c>
-      <c r="H25" t="s">
-        <v>221</v>
-      </c>
-      <c r="I25" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B26" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="G26" t="s">
-        <v>244</v>
-      </c>
-      <c r="H26" t="s">
-        <v>221</v>
-      </c>
-      <c r="I26" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E27" s="14"/>
-      <c r="G27" t="s">
-        <v>244</v>
-      </c>
-      <c r="H27" t="s">
-        <v>221</v>
-      </c>
-      <c r="I27" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B28" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="G28" t="s">
-        <v>246</v>
-      </c>
-      <c r="H28" t="s">
-        <v>221</v>
-      </c>
-      <c r="I28" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B29" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="G29" t="s">
-        <v>247</v>
-      </c>
-      <c r="H29" t="s">
-        <v>221</v>
-      </c>
-      <c r="I29" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B30" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D30" s="3">
-        <v>2004</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G30" t="s">
-        <v>248</v>
-      </c>
-      <c r="H30" t="s">
-        <v>221</v>
-      </c>
-      <c r="I30">
-        <v>2004</v>
-      </c>
-      <c r="J30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B31" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2004</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G31" t="s">
-        <v>248</v>
-      </c>
-      <c r="H31" t="s">
-        <v>221</v>
-      </c>
-      <c r="I31">
-        <v>2004</v>
-      </c>
-      <c r="J31" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B32" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="G32" t="s">
-        <v>249</v>
-      </c>
-      <c r="H32" t="s">
-        <v>250</v>
-      </c>
-      <c r="I32" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B33" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="G33" t="s">
-        <v>252</v>
-      </c>
-      <c r="H33" t="s">
-        <v>221</v>
-      </c>
-      <c r="I33" t="s">
-        <v>253</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -4378,27 +3708,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6D714A-5497-420A-9146-5640EA73F0F4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4415,29 +3750,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>